--- a/Dependencies/Analysis_Outputs/Takasugi_2024/Precursor_RAAS_byAAS_alldatasets.xlsx
+++ b/Dependencies/Analysis_Outputs/Takasugi_2024/Precursor_RAAS_byAAS_alldatasets.xlsx
@@ -468,213 +468,199 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>W to D</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>-1.722636724034003</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-2.328690457145978</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-0.6253722930975758</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-1.402210999989914</v>
-      </c>
+          <t>E to N</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>-3.004471441837086</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-1.030732723063158</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-2.691516411503164</v>
-      </c>
+        <v>-0.4699090525340123</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Y to F</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0.5106078165789603</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>A to P</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>-3.771141297540485</v>
+      </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>0.3731957164374532</v>
+      </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>H to Q</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+          <t>A to S</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>-1.653611732509545</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-2.459914065544374</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.899103714087661</v>
+      </c>
       <c r="E4" t="n">
-        <v>-2.55794481577012</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+        <v>-1.86713275228325</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-1.381297706019851</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-2.399248944612595</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-1.978893620843214</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>E to D</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>-1.695488176301252</v>
-      </c>
-      <c r="C5" t="n">
-        <v>2.01613840163154</v>
-      </c>
+          <t>H to D</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>-1.514162905069868</v>
+        <v>-2.483583783071391</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6630539921802125</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.06030790879759981</v>
-      </c>
+        <v>-1.855115502100755</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>-1.30711732865362</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-2.10002842790094</v>
-      </c>
+        <v>-2.619226660244165</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>T to S</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>-0.8985488438430838</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.1859037582748287</v>
-      </c>
+          <t>N to L</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>-0.0820707001536027</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.128130571944069</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.3570625255991471</v>
-      </c>
+        <v>-3.364352568501581</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="n">
-        <v>-1.210849890401181</v>
-      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>M to L</t>
+          <t>L to A</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4847833444086794</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.2188790850080173</v>
-      </c>
+        <v>-1.85169555311221</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="n">
-        <v>1.075310745863635</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-0.4014427711549966</v>
-      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>-0.1435421679693263</v>
+        <v>-3.416972568595083</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>F to L</t>
+          <t>F to D</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-3.948831480479853</v>
+        <v>-3.309204457370565</v>
       </c>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" t="n">
-        <v>-3.889766250552038</v>
-      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="n">
-        <v>-3.793268283296064</v>
-      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>N to A</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>A to N</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>-2.113385165834488</v>
+      </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="n">
-        <v>-0.08087624280675883</v>
-      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>T to L</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+          <t>T to N</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.6760035906907884</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-1.136963870611551</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-1.198406733572394</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-1.956212415169413</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-2.699279618199955</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-2.755995412246732</v>
+      </c>
       <c r="H10" t="n">
-        <v>-2.505175572011161</v>
+        <v>-1.668023383360149</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>N to V</t>
+          <t>V to M</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
-      <c r="C11" t="n">
-        <v>0.6443620676802376</v>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>0.5084920308060468</v>
+      </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>S to Y</t>
+          <t>Q to L</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -682,223 +668,269 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="n">
-        <v>-2.339354789574339</v>
-      </c>
+      <c r="G12" t="n">
+        <v>0.2919444794646509</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>R to D</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="n">
-        <v>-2.608319596653854</v>
-      </c>
+          <t>M to L</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.4847833444086794</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.2188790850080173</v>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>1.075310745863635</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.4014427711549966</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.1435421679693263</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Q to T</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
+          <t>G to A</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>-2.274956495453408</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-1.568698996570776</v>
+      </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>-0.1798237950870692</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.4675582490927363</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-3.661094973247053</v>
+      </c>
       <c r="H14" t="n">
-        <v>1.086464388557685</v>
+        <v>-1.646884689977292</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>S to Q</t>
+          <t>Y to D</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.650976608770522</v>
+        <v>-3.167267514942288</v>
       </c>
       <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>-3.131598267472652</v>
+      </c>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="n">
-        <v>0.2326868042681486</v>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>G to S</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
+          <t>T to S</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>-0.8985488438430838</v>
+      </c>
       <c r="C16" t="n">
-        <v>-2.656637789262418</v>
-      </c>
-      <c r="D16" t="inlineStr"/>
+        <v>0.1859037582748287</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.0820707001536027</v>
+      </c>
       <c r="E16" t="n">
-        <v>-0.7409616256272265</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
+        <v>0.128130571944069</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.3570625255991471</v>
+      </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>-0.8665381240807005</v>
+        <v>-1.210849890401181</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>A to G</t>
+          <t>Q to N</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>-0.3259610591989811</v>
-      </c>
-      <c r="E17" t="n">
-        <v>-2.413429801330959</v>
-      </c>
+        <v>-0.05838252838268451</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>-1.903858474525991</v>
+      </c>
       <c r="H17" t="n">
-        <v>-0.2912372794970885</v>
+        <v>-1.381444765737683</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>N to M</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
+          <t>Q to A</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>-0.2000620417383523</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.474415229829117</v>
+      </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>-2.61347715481835</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-1.12695207243301</v>
-      </c>
-      <c r="G18" t="inlineStr"/>
+        <v>0.1349921974942554</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>-3.920718418177883</v>
+      </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>G to V</t>
+          <t>Y to V</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="n">
+        <v>-1.510120646029611</v>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>-3.474030511697374</v>
+        <v>-2.466257082351836</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>N to L</t>
+          <t>P to A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>-3.364352568501581</v>
+        <v>-1.107063917181411</v>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>0.2017411604221624</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.0554437364283121</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Q to G</t>
+          <t>V to L</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-4.617351748881742</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
+        <v>-2.302471589881319</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.3986760515835863</v>
+      </c>
       <c r="D21" t="n">
-        <v>-2.568712116055132</v>
+        <v>-1.429449696060894</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.080497519684329</v>
+        <v>-2.525290621535615</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.041909812876552</v>
-      </c>
-      <c r="G21" t="inlineStr"/>
+        <v>-3.334997402006044</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-3.936879460319163</v>
+      </c>
       <c r="H21" t="n">
-        <v>-1.778417401343809</v>
+        <v>-1.006247239572388</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>M to N</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
+          <t>S to N</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>-0.248457796440002</v>
+      </c>
       <c r="C22" t="n">
-        <v>-1.749751165507866</v>
-      </c>
-      <c r="D22" t="inlineStr"/>
+        <v>-4.224546763368163</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-3.345708569075381</v>
+      </c>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>-0.746232156782947</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-2.4629972214545</v>
+      </c>
       <c r="H22" t="n">
-        <v>-1.045678761696865</v>
+        <v>-1.350890689929132</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>W to S</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>-2.704278926893959</v>
-      </c>
+          <t>G to E</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+      <c r="F23" t="n">
+        <v>-3.768338895412208</v>
+      </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>A to P</t>
+          <t>N to M</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
-      <c r="C24" t="n">
-        <v>-3.771141297540485</v>
-      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="n">
+        <v>-2.61347715481835</v>
+      </c>
       <c r="F24" t="n">
-        <v>0.3731957164374532</v>
+        <v>-1.12695207243301</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
@@ -906,167 +938,157 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>W to N</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>-2.312505496465151</v>
-      </c>
+          <t>A to G</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="n">
-        <v>-0.8829650871445479</v>
+        <v>-0.3259610591989811</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.509933880113272</v>
+        <v>-2.413429801330959</v>
       </c>
       <c r="F25" t="inlineStr"/>
-      <c r="G25" t="n">
-        <v>-1.969879407604043</v>
-      </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="n">
+        <v>-0.2912372794970885</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>N to T</t>
+          <t>E to G</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="n">
-        <v>0.2789321165301343</v>
-      </c>
-      <c r="F26" t="inlineStr"/>
+      <c r="C26" t="n">
+        <v>-0.9697446546504551</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-1.488929475196924</v>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="n">
+        <v>-1.144739022853206</v>
+      </c>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="n">
+        <v>-0.9031529500178701</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>D to M</t>
+          <t>V to Y</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
-      <c r="D27" t="n">
-        <v>-0.2648066704967862</v>
-      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
+      <c r="F27" t="n">
+        <v>1.595115076554973</v>
+      </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>L to S</t>
+          <t>L to T</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>-0.01083246424702433</v>
+        <v>1.751809822922723</v>
       </c>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="n">
-        <v>1.632168232382287</v>
-      </c>
-      <c r="F28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="n">
+        <v>1.863047732651588</v>
+      </c>
       <c r="G28" t="n">
-        <v>-1.60820929705348</v>
-      </c>
-      <c r="H28" t="n">
-        <v>2.389617897730931</v>
-      </c>
+        <v>0.00927342209330112</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>A to S</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>-1.653611732509545</v>
-      </c>
+          <t>Y to E</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>-2.459914065544374</v>
-      </c>
-      <c r="D29" t="n">
-        <v>-1.899103714087661</v>
-      </c>
-      <c r="E29" t="n">
-        <v>-1.86713275228325</v>
-      </c>
-      <c r="F29" t="n">
-        <v>-1.381297706019851</v>
-      </c>
-      <c r="G29" t="n">
-        <v>-2.399248944612595</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-1.978893620843214</v>
-      </c>
+        <v>0.6137304556272241</v>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Y to D</t>
+          <t>V to T</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-3.167267514942288</v>
-      </c>
-      <c r="C30" t="inlineStr"/>
+        <v>-2.034111829240633</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-2.144093010176558</v>
+      </c>
       <c r="D30" t="n">
-        <v>-3.131598267472652</v>
+        <v>-1.02678063256853</v>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+      <c r="G30" t="n">
+        <v>-0.5733553683658663</v>
+      </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>V to N</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>-2.233468881978405</v>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>M to N</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="n">
+        <v>-1.749751165507866</v>
+      </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>-1.045678761696865</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>T to G</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>-2.637534625954949</v>
-      </c>
+          <t>Q to T</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
-      <c r="D32" t="n">
-        <v>-3.360101463103227</v>
-      </c>
-      <c r="E32" t="n">
-        <v>-3.642308061020011</v>
-      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
-      <c r="G32" t="n">
-        <v>-3.160644640988411</v>
-      </c>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="n">
+        <v>1.086464388557685</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>H to E</t>
+          <t>P to H</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1074,183 +1096,145 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="n">
-        <v>-0.8498319899764668</v>
-      </c>
+      <c r="G33" t="n">
+        <v>-2.987764698876072</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>A to L</t>
+          <t>S to L</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-2.802850110453551</v>
+        <v>-1.188565431579376</v>
       </c>
       <c r="C34" t="inlineStr"/>
-      <c r="D34" t="n">
-        <v>-2.623247090950027</v>
-      </c>
-      <c r="E34" t="n">
-        <v>-2.187321493283763</v>
-      </c>
-      <c r="F34" t="n">
-        <v>-1.070850200713596</v>
-      </c>
-      <c r="G34" t="n">
-        <v>-3.923012433266679</v>
-      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>-2.782519413630628</v>
+        <v>0.3041449342967618</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>G to D</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>-1.92518725805567</v>
-      </c>
-      <c r="C35" t="n">
-        <v>-2.100923042509431</v>
-      </c>
+          <t>D to M</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="n">
-        <v>-2.604501883894249</v>
-      </c>
-      <c r="E35" t="n">
-        <v>-1.988311868634468</v>
-      </c>
-      <c r="F35" t="n">
-        <v>-2.746981662382514</v>
-      </c>
-      <c r="G35" t="n">
-        <v>-2.073661861816529</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-2.010681456347183</v>
-      </c>
+        <v>-0.2648066704967862</v>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>T to N</t>
+          <t>V to N</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.6760035906907884</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-1.136963870611551</v>
-      </c>
-      <c r="D36" t="n">
-        <v>-1.198406733572394</v>
-      </c>
-      <c r="E36" t="n">
-        <v>-1.956212415169413</v>
-      </c>
-      <c r="F36" t="n">
-        <v>-2.699279618199955</v>
-      </c>
-      <c r="G36" t="n">
-        <v>-2.755995412246732</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-1.668023383360149</v>
-      </c>
+        <v>-2.233468881978405</v>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>A to D</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="n">
-        <v>-0.2391723610689255</v>
-      </c>
+          <t>G to Q</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>-0.6347909395399469</v>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="n">
-        <v>-0.7494146671336924</v>
-      </c>
-      <c r="F37" t="n">
-        <v>-1.900064868836055</v>
-      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>A to N</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>-2.113385165834488</v>
-      </c>
+          <t>N to A</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="H38" t="n">
+        <v>-0.08087624280675883</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>G to E</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
+          <t>V to A</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>-0.8538128368955641</v>
+      </c>
       <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="n">
+        <v>-0.8037119226970224</v>
+      </c>
       <c r="E39" t="inlineStr"/>
-      <c r="F39" t="n">
-        <v>-3.768338895412208</v>
-      </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="n">
+        <v>-0.6914815164071293</v>
+      </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>A to V</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>0.6743193305069911</v>
-      </c>
+          <t>L to S</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>-3.27065275146723</v>
-      </c>
-      <c r="D40" t="n">
-        <v>-3.049546900640282</v>
-      </c>
+        <v>-0.01083246424702433</v>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="n">
-        <v>-3.876919833538941</v>
-      </c>
-      <c r="F40" t="n">
-        <v>-1.477788468049074</v>
-      </c>
+        <v>1.632168232382287</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
-        <v>-3.40090308620753</v>
+        <v>-1.60820929705348</v>
       </c>
       <c r="H40" t="n">
-        <v>-3.063936049229842</v>
+        <v>2.389617897730931</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>G to N</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="n">
-        <v>0.3710255970720046</v>
-      </c>
+          <t>Y to F</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0.5106078165789603</v>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
@@ -1260,186 +1244,190 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>P to Q</t>
+          <t>W to D</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-2.805861571055532</v>
-      </c>
-      <c r="C42" t="inlineStr"/>
+        <v>-1.722636724034003</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-2.328690457145978</v>
+      </c>
       <c r="D42" t="n">
-        <v>-3.004153195922547</v>
+        <v>-0.6253722930975758</v>
       </c>
       <c r="E42" t="n">
-        <v>-1.065335126312458</v>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+        <v>-1.402210999989914</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-3.004471441837086</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-1.030732723063158</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-2.691516411503164</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>S to G</t>
+          <t>A to E</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.8717497641459152</v>
-      </c>
-      <c r="C43" t="n">
-        <v>-2.600027978513686</v>
-      </c>
+        <v>-2.683048128171823</v>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="n">
-        <v>-0.9467417255990334</v>
-      </c>
-      <c r="E43" t="n">
-        <v>-0.6757723879317308</v>
-      </c>
-      <c r="F43" t="n">
-        <v>-0.3099697435070426</v>
-      </c>
+        <v>-2.192556222380435</v>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
-        <v>-3.549755960315697</v>
+        <v>-2.153319950147123</v>
       </c>
       <c r="H43" t="n">
-        <v>-1.694675476216068</v>
+        <v>-0.5836829254647322</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>P to A</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
+          <t>A to V</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0.6743193305069911</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-3.27065275146723</v>
+      </c>
       <c r="D44" t="n">
-        <v>-1.107063917181411</v>
-      </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
+        <v>-3.049546900640282</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-3.876919833538941</v>
+      </c>
+      <c r="F44" t="n">
+        <v>-1.477788468049074</v>
+      </c>
       <c r="G44" t="n">
-        <v>0.2017411604221624</v>
+        <v>-3.40090308620753</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.0554437364283121</v>
+        <v>-3.063936049229842</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>V to Y</t>
+          <t>V to E</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="n">
+        <v>-0.9629208311347879</v>
+      </c>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="n">
-        <v>1.595115076554973</v>
-      </c>
-      <c r="G45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="n">
+        <v>-1.425100153146231</v>
+      </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>V to P</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>-2.423602075442781</v>
-      </c>
-      <c r="C46" t="n">
-        <v>-3.088886269346305</v>
-      </c>
-      <c r="D46" t="n">
-        <v>-2.963804444706708</v>
-      </c>
-      <c r="E46" t="n">
-        <v>-2.785444055044065</v>
-      </c>
-      <c r="F46" t="n">
-        <v>-3.134677395087106</v>
-      </c>
+          <t>M to P</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
-        <v>-2.719089356968935</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-3.010332173473242</v>
-      </c>
+        <v>-1.748834774308884</v>
+      </c>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>T to A</t>
+          <t>H to N</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-2.008557789268514</v>
-      </c>
-      <c r="C47" t="n">
-        <v>-2.770774191271241</v>
-      </c>
+        <v>-3.033578741829277</v>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="n">
-        <v>-1.615861025003912</v>
-      </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="n">
-        <v>-2.446230806818669</v>
-      </c>
-      <c r="G47" t="inlineStr"/>
+        <v>-3.03220632419723</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-2.786244013031539</v>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="n">
+        <v>-2.274450459396264</v>
+      </c>
       <c r="H47" t="n">
-        <v>-0.5546555287971635</v>
+        <v>-3.76843322370768</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>V to Q</t>
+          <t>W to N</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-2.054849408012198</v>
+        <v>-2.312505496465151</v>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="n">
-        <v>-0.6779423599503973</v>
+        <v>-0.8829650871445479</v>
       </c>
       <c r="E48" t="n">
-        <v>-2.201985685495538</v>
+        <v>-2.509933880113272</v>
       </c>
       <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="n">
+        <v>-1.969879407604043</v>
+      </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>P to H</t>
+          <t>P to D</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>-2.560987937322469</v>
+      </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
-      <c r="G49" t="n">
-        <v>-2.987764698876072</v>
-      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>W to Y</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
+          <t>Y to T</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0.4030353674958173</v>
+      </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="n">
-        <v>-0.2897817151993893</v>
+        <v>-0.2490438732309269</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
@@ -1448,310 +1436,306 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>P to T</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>0.005988936812045846</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-1.521099053021751</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0.2168144388987391</v>
-      </c>
+          <t>W to Y</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="n">
-        <v>-0.3273703705333563</v>
-      </c>
-      <c r="F51" t="n">
-        <v>-1.552935694434832</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0.2195690271506754</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-0.6401930651142367</v>
-      </c>
+        <v>-0.2897817151993893</v>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>G to Q</t>
+          <t>F to L</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.6347909395399469</v>
+        <v>-3.948831480479853</v>
       </c>
       <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="n">
+        <v>-3.889766250552038</v>
+      </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="H52" t="n">
+        <v>-3.793268283296064</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>M to P</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr"/>
+          <t>D to S</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>-3.226243219394461</v>
+      </c>
+      <c r="C53" t="n">
+        <v>-3.256687188348717</v>
+      </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
-        <v>-1.748834774308884</v>
-      </c>
-      <c r="H53" t="inlineStr"/>
+        <v>-2.644600810825756</v>
+      </c>
+      <c r="H53" t="n">
+        <v>-2.44725505704062</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>G to T</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
+          <t>T to D</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>-2.403180820213024</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-3.357326728676407</v>
+      </c>
+      <c r="D54" t="n">
+        <v>-2.090358928481429</v>
+      </c>
       <c r="E54" t="n">
-        <v>-2.577337431206515</v>
-      </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+        <v>-1.98053688359063</v>
+      </c>
+      <c r="F54" t="n">
+        <v>-2.116820017899765</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-1.985760119116385</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-2.651831876495732</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>H to D</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
+          <t>Q to G</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>-4.617351748881742</v>
+      </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="n">
-        <v>-2.483583783071391</v>
+        <v>-2.568712116055132</v>
       </c>
       <c r="E55" t="n">
-        <v>-1.855115502100755</v>
-      </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="n">
-        <v>-2.619226660244165</v>
-      </c>
-      <c r="H55" t="inlineStr"/>
+        <v>-1.080497519684329</v>
+      </c>
+      <c r="F55" t="n">
+        <v>-3.041909812876552</v>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="n">
+        <v>-1.778417401343809</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>E to A</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="n">
-        <v>-2.568566610168357</v>
-      </c>
+          <t>W to A</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>-2.339776212129112</v>
+      </c>
+      <c r="C56" t="n">
+        <v>-2.572863712570823</v>
+      </c>
+      <c r="D56" t="n">
+        <v>-1.369833728023988</v>
+      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="n">
+        <v>-1.523642807889777</v>
+      </c>
+      <c r="H56" t="n">
+        <v>-3.452306971230587</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>E to L</t>
+          <t>T to L</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
-      <c r="F57" t="n">
-        <v>1.054715408594351</v>
-      </c>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="H57" t="n">
+        <v>-2.505175572011161</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>T to D</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>-2.403180820213024</v>
-      </c>
-      <c r="C58" t="n">
-        <v>-3.357326728676407</v>
-      </c>
-      <c r="D58" t="n">
-        <v>-2.090358928481429</v>
-      </c>
-      <c r="E58" t="n">
-        <v>-1.98053688359063</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-2.116820017899765</v>
-      </c>
+          <t>L to P</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="n">
-        <v>-1.985760119116385</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-2.651831876495732</v>
-      </c>
+        <v>-0.9785445819541522</v>
+      </c>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>G to A</t>
+          <t>S to G</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-2.274956495453408</v>
+        <v>-0.8717497641459152</v>
       </c>
       <c r="C59" t="n">
-        <v>-1.568698996570776</v>
-      </c>
-      <c r="D59" t="inlineStr"/>
+        <v>-2.600027978513686</v>
+      </c>
+      <c r="D59" t="n">
+        <v>-0.9467417255990334</v>
+      </c>
       <c r="E59" t="n">
-        <v>-0.1798237950870692</v>
+        <v>-0.6757723879317308</v>
       </c>
       <c r="F59" t="n">
-        <v>0.4675582490927363</v>
+        <v>-0.3099697435070426</v>
       </c>
       <c r="G59" t="n">
-        <v>-3.661094973247053</v>
+        <v>-3.549755960315697</v>
       </c>
       <c r="H59" t="n">
-        <v>-1.646884689977292</v>
+        <v>-1.694675476216068</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>V to A</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>-0.8538128368955641</v>
-      </c>
+          <t>N to T</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr"/>
-      <c r="D60" t="n">
-        <v>-0.8037119226970224</v>
-      </c>
-      <c r="E60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="n">
+        <v>0.2789321165301343</v>
+      </c>
       <c r="F60" t="inlineStr"/>
-      <c r="G60" t="n">
-        <v>-0.6914815164071293</v>
-      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>Y to V</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
+          <t>A to T</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>-1.359588084237156</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-1.703866794664202</v>
+      </c>
+      <c r="D61" t="n">
+        <v>-1.167796588823167</v>
+      </c>
       <c r="E61" t="n">
-        <v>-1.510120646029611</v>
-      </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="n">
-        <v>-2.466257082351836</v>
-      </c>
-      <c r="H61" t="inlineStr"/>
+        <v>-0.751593702445349</v>
+      </c>
+      <c r="F61" t="n">
+        <v>-1.100616422917592</v>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="n">
+        <v>-1.189664748651732</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>H to N</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>-3.033578741829277</v>
-      </c>
+          <t>P to G</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
-      <c r="D62" t="n">
-        <v>-3.03220632419723</v>
-      </c>
-      <c r="E62" t="n">
-        <v>-2.786244013031539</v>
-      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
-        <v>-2.274450459396264</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-3.76843322370768</v>
-      </c>
+        <v>-2.786671966027997</v>
+      </c>
+      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>S to N</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>-0.248457796440002</v>
-      </c>
-      <c r="C63" t="n">
-        <v>-4.224546763368163</v>
-      </c>
+          <t>R to D</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="n">
-        <v>-3.345708569075381</v>
+        <v>-2.608319596653854</v>
       </c>
       <c r="E63" t="inlineStr"/>
-      <c r="F63" t="n">
-        <v>-0.746232156782947</v>
-      </c>
-      <c r="G63" t="n">
-        <v>-2.4629972214545</v>
-      </c>
-      <c r="H63" t="n">
-        <v>-1.350890689929132</v>
-      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>E to N</t>
+          <t>G to S</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr"/>
+      <c r="C64" t="n">
+        <v>-2.656637789262418</v>
+      </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="n">
-        <v>-0.4699090525340123</v>
-      </c>
+      <c r="E64" t="n">
+        <v>-0.7409616256272265</v>
+      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="H64" t="n">
+        <v>-0.8665381240807005</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>A to E</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>-2.683048128171823</v>
-      </c>
+          <t>G to T</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" t="n">
-        <v>-2.192556222380435</v>
-      </c>
-      <c r="E65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="n">
+        <v>-2.577337431206515</v>
+      </c>
       <c r="F65" t="inlineStr"/>
-      <c r="G65" t="n">
-        <v>-2.153319950147123</v>
-      </c>
-      <c r="H65" t="n">
-        <v>-0.5836829254647322</v>
-      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
@@ -1772,233 +1756,237 @@
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>V to M</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
+          <t>W to S</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>-2.704278926893959</v>
+      </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
-      <c r="G67" t="n">
-        <v>0.5084920308060468</v>
-      </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>L to Q</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
+          <t>P to Q</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>-2.805861571055532</v>
+      </c>
       <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="n">
+        <v>-3.004153195922547</v>
+      </c>
       <c r="E68" t="n">
-        <v>-1.194890071006058</v>
+        <v>-1.065335126312458</v>
       </c>
       <c r="F68" t="inlineStr"/>
-      <c r="G68" t="n">
-        <v>-1.742118726251878</v>
-      </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>Q to N</t>
+          <t>E to L</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr"/>
-      <c r="D69" t="n">
-        <v>-0.05838252838268451</v>
-      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="n">
-        <v>-1.903858474525991</v>
-      </c>
-      <c r="H69" t="n">
-        <v>-1.381444765737683</v>
-      </c>
+      <c r="F69" t="n">
+        <v>1.054715408594351</v>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>T to V</t>
+          <t>P to L</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="n">
+        <v>-3.905384031657701</v>
+      </c>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="n">
-        <v>-3.393364726437454</v>
-      </c>
+      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>W to A</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>-2.339776212129112</v>
-      </c>
-      <c r="C71" t="n">
-        <v>-2.572863712570823</v>
-      </c>
+          <t>E to T</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="n">
-        <v>-1.369833728023988</v>
-      </c>
-      <c r="E71" t="inlineStr"/>
+        <v>-3.123968025683438</v>
+      </c>
+      <c r="E71" t="n">
+        <v>-3.296960640065991</v>
+      </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="n">
-        <v>-1.523642807889777</v>
+        <v>-3.202980143924978</v>
       </c>
       <c r="H71" t="n">
-        <v>-3.452306971230587</v>
+        <v>-3.451097770458866</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>L to T</t>
+          <t>S to Y</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
-      <c r="C72" t="n">
-        <v>1.751809822922723</v>
-      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
-      <c r="F72" t="n">
-        <v>1.863047732651588</v>
-      </c>
-      <c r="G72" t="n">
-        <v>0.00927342209330112</v>
-      </c>
-      <c r="H72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="n">
+        <v>-2.339354789574339</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>S to L</t>
+          <t>T to G</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.188565431579376</v>
+        <v>-2.637534625954949</v>
       </c>
       <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
+      <c r="D73" t="n">
+        <v>-3.360101463103227</v>
+      </c>
+      <c r="E73" t="n">
+        <v>-3.642308061020011</v>
+      </c>
       <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="n">
-        <v>0.3041449342967618</v>
-      </c>
+      <c r="G73" t="n">
+        <v>-3.160644640988411</v>
+      </c>
+      <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>Y to E</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr"/>
+          <t>T to A</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>-2.008557789268514</v>
+      </c>
       <c r="C74" t="n">
-        <v>0.6137304556272241</v>
-      </c>
-      <c r="D74" t="inlineStr"/>
+        <v>-2.770774191271241</v>
+      </c>
+      <c r="D74" t="n">
+        <v>-1.615861025003912</v>
+      </c>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
+      <c r="F74" t="n">
+        <v>-2.446230806818669</v>
+      </c>
       <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="H74" t="n">
+        <v>-0.5546555287971635</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>Q to A</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>-0.2000620417383523</v>
-      </c>
-      <c r="C75" t="n">
-        <v>0.474415229829117</v>
-      </c>
+          <t>E to A</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="n">
-        <v>0.1349921974942554</v>
+        <v>-2.568566610168357</v>
       </c>
       <c r="F75" t="inlineStr"/>
-      <c r="G75" t="n">
-        <v>-3.920718418177883</v>
-      </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>E to G</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr"/>
+          <t>E to D</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>-1.695488176301252</v>
+      </c>
       <c r="C76" t="n">
-        <v>-0.9697446546504551</v>
+        <v>2.01613840163154</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.488929475196924</v>
-      </c>
-      <c r="E76" t="inlineStr"/>
+        <v>-1.514162905069868</v>
+      </c>
+      <c r="E76" t="n">
+        <v>-0.6630539921802125</v>
+      </c>
       <c r="F76" t="n">
-        <v>-1.144739022853206</v>
-      </c>
-      <c r="G76" t="inlineStr"/>
+        <v>0.06030790879759981</v>
+      </c>
+      <c r="G76" t="n">
+        <v>-1.30711732865362</v>
+      </c>
       <c r="H76" t="n">
-        <v>-0.9031529500178701</v>
+        <v>-2.10002842790094</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>P to D</t>
+          <t>L to Q</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr"/>
-      <c r="D77" t="n">
-        <v>-2.560987937322469</v>
-      </c>
-      <c r="E77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="n">
+        <v>-1.194890071006058</v>
+      </c>
       <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
+      <c r="G77" t="n">
+        <v>-1.742118726251878</v>
+      </c>
       <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>N to G</t>
+          <t>P to S</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="n">
-        <v>-0.2495826010211096</v>
-      </c>
-      <c r="F78" t="n">
-        <v>-1.045868279855427</v>
-      </c>
+      <c r="D78" t="n">
+        <v>0.147834489708815</v>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>P to G</t>
+          <t>D to A</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -2007,7 +1995,7 @@
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
-        <v>-2.786671966027997</v>
+        <v>-2.02379695041923</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -2030,209 +2018,227 @@
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>E to T</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr"/>
+          <t>P to T</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>0.005988936812045846</v>
+      </c>
+      <c r="C81" t="n">
+        <v>-1.521099053021751</v>
+      </c>
       <c r="D81" t="n">
-        <v>-3.123968025683438</v>
+        <v>0.2168144388987391</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.296960640065991</v>
-      </c>
-      <c r="F81" t="inlineStr"/>
+        <v>-0.3273703705333563</v>
+      </c>
+      <c r="F81" t="n">
+        <v>-1.552935694434832</v>
+      </c>
       <c r="G81" t="n">
-        <v>-3.202980143924978</v>
+        <v>0.2195690271506754</v>
       </c>
       <c r="H81" t="n">
-        <v>-3.451097770458866</v>
+        <v>-0.6401930651142367</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>D to A</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr"/>
-      <c r="C82" t="inlineStr"/>
+          <t>L to V</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>2.050502008927432</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-1.449770635901166</v>
+      </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
-      <c r="G82" t="n">
-        <v>-2.02379695041923</v>
-      </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>P to L</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
-      <c r="C83" t="inlineStr"/>
+          <t>G to D</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>-1.92518725805567</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-2.100923042509431</v>
+      </c>
       <c r="D83" t="n">
-        <v>-3.905384031657701</v>
-      </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+        <v>-2.604501883894249</v>
+      </c>
+      <c r="E83" t="n">
+        <v>-1.988311868634468</v>
+      </c>
+      <c r="F83" t="n">
+        <v>-2.746981662382514</v>
+      </c>
+      <c r="G83" t="n">
+        <v>-2.073661861816529</v>
+      </c>
+      <c r="H83" t="n">
+        <v>-2.010681456347183</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>V to L</t>
+          <t>V to Q</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-2.302471589881319</v>
-      </c>
-      <c r="C84" t="n">
-        <v>0.3986760515835863</v>
-      </c>
+        <v>-2.054849408012198</v>
+      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="n">
-        <v>-1.429449696060894</v>
+        <v>-0.6779423599503973</v>
       </c>
       <c r="E84" t="n">
-        <v>-2.525290621535615</v>
-      </c>
-      <c r="F84" t="n">
-        <v>-3.334997402006044</v>
-      </c>
-      <c r="G84" t="n">
-        <v>-3.936879460319163</v>
-      </c>
-      <c r="H84" t="n">
-        <v>-1.006247239572388</v>
-      </c>
+        <v>-2.201985685495538</v>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>Y to T</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>0.4030353674958173</v>
-      </c>
+          <t>N to G</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="n">
-        <v>-0.2490438732309269</v>
-      </c>
-      <c r="F85" t="inlineStr"/>
+        <v>-0.2495826010211096</v>
+      </c>
+      <c r="F85" t="n">
+        <v>-1.045868279855427</v>
+      </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>P to S</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr"/>
-      <c r="C86" t="inlineStr"/>
+          <t>V to P</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>-2.423602075442781</v>
+      </c>
+      <c r="C86" t="n">
+        <v>-3.088886269346305</v>
+      </c>
       <c r="D86" t="n">
-        <v>0.147834489708815</v>
-      </c>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+        <v>-2.963804444706708</v>
+      </c>
+      <c r="E86" t="n">
+        <v>-2.785444055044065</v>
+      </c>
+      <c r="F86" t="n">
+        <v>-3.134677395087106</v>
+      </c>
+      <c r="G86" t="n">
+        <v>-2.719089356968935</v>
+      </c>
+      <c r="H86" t="n">
+        <v>-3.010332173473242</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>Q to L</t>
+          <t>T to V</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="n">
-        <v>0.2919444794646509</v>
-      </c>
+      <c r="F87" t="n">
+        <v>-3.393364726437454</v>
+      </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>A to T</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>-1.359588084237156</v>
-      </c>
+          <t>N to V</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>-1.703866794664202</v>
-      </c>
-      <c r="D88" t="n">
-        <v>-1.167796588823167</v>
-      </c>
-      <c r="E88" t="n">
-        <v>-0.751593702445349</v>
-      </c>
-      <c r="F88" t="n">
-        <v>-1.100616422917592</v>
-      </c>
+        <v>0.6443620676802376</v>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
-      <c r="H88" t="n">
-        <v>-1.189664748651732</v>
-      </c>
+      <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>V to T</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>-2.034111829240633</v>
-      </c>
-      <c r="C89" t="n">
-        <v>-2.144093010176558</v>
-      </c>
-      <c r="D89" t="n">
-        <v>-1.02678063256853</v>
-      </c>
+          <t>H to E</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
-      <c r="G89" t="n">
-        <v>-0.5733553683658663</v>
-      </c>
-      <c r="H89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="n">
+        <v>-0.8498319899764668</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>L to P</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
+          <t>A to L</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>-2.802850110453551</v>
+      </c>
       <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
+      <c r="D90" t="n">
+        <v>-2.623247090950027</v>
+      </c>
+      <c r="E90" t="n">
+        <v>-2.187321493283763</v>
+      </c>
+      <c r="F90" t="n">
+        <v>-1.070850200713596</v>
+      </c>
       <c r="G90" t="n">
-        <v>-0.9785445819541522</v>
-      </c>
-      <c r="H90" t="inlineStr"/>
+        <v>-3.923012433266679</v>
+      </c>
+      <c r="H90" t="n">
+        <v>-2.782519413630628</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>F to D</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>-3.309204457370565</v>
-      </c>
-      <c r="C91" t="inlineStr"/>
+          <t>G to N</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="n">
+        <v>0.3710255970720046</v>
+      </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
@@ -2242,75 +2248,69 @@
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>D to S</t>
+          <t>S to Q</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-3.226243219394461</v>
-      </c>
-      <c r="C92" t="n">
-        <v>-3.256687188348717</v>
-      </c>
+        <v>0.650976608770522</v>
+      </c>
+      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="n">
-        <v>-2.644600810825756</v>
-      </c>
-      <c r="H92" t="n">
-        <v>-2.44725505704062</v>
-      </c>
+      <c r="F92" t="n">
+        <v>0.2326868042681486</v>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>V to E</t>
+          <t>A to D</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
-      <c r="C93" t="inlineStr"/>
-      <c r="D93" t="n">
-        <v>-0.9629208311347879</v>
-      </c>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="n">
-        <v>-1.425100153146231</v>
-      </c>
+      <c r="C93" t="n">
+        <v>-0.2391723610689255</v>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="n">
+        <v>-0.7494146671336924</v>
+      </c>
+      <c r="F93" t="n">
+        <v>-1.900064868836055</v>
+      </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>L to A</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>-1.85169555311221</v>
-      </c>
+          <t>G to V</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="n">
-        <v>-3.416972568595083</v>
-      </c>
+      <c r="G94" t="n">
+        <v>-3.474030511697374</v>
+      </c>
+      <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>L to V</t>
-        </is>
-      </c>
-      <c r="B95" t="n">
-        <v>2.050502008927432</v>
-      </c>
-      <c r="C95" t="n">
-        <v>-1.449770635901166</v>
-      </c>
+          <t>H to Q</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
+      <c r="E95" t="n">
+        <v>-2.55794481577012</v>
+      </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
